--- a/docs/bulk-employee-upload/employee-import-sample.xlsx
+++ b/docs/bulk-employee-upload/employee-import-sample.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>SecurePass123!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>plan-001</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TechPass456!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>plan-001</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>DevPass789!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>plan-002</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>FinPass123!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>plan-001</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>HRPass456!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>plan-003</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>SalesPass789!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>plan-002</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ITPass123!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>plan-001</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>DesignPass456!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>plan-002</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>LogisPass789!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>plan-001</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ProdPass123!</t>
+          <t>Pass1234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>plan-003</t>
+          <t>61683d5b-16d4-41a4-b7c4-46551fc6fc61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
